--- a/output/日本赤十字社医療センター_随意契約_X線関連.xlsx
+++ b/output/日本赤十字社医療センター_随意契約_X線関連.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>血管撮影装置の新設に伴う電気設備工事（一式）</t>
+          <t>据置型デジタル式X線血管造影診断装置（Artis zee BA）（シーメンス）にかかる保守契約の締結について</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
@@ -585,33 +585,119 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>令和7年2月7日</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>シーメンスヘルスケア株式会社東京都品川区大崎1-11-1</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>１９，３１８，２００円</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.med.jrc.or.jp/Portals/0/resources/chotatsu/zuikei/zuikei_202404q.pdf</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>血管撮影（CVS、アンギオ）</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>血管撮影装置の新設に伴う電気設備工事（一式）</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>東京都渋谷区広尾4-1-22日本赤十字社医療センター契約管財課</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>令和5年9月26日</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>TMES株式会社東京都港区芝4-13-23MS芝浦ビル8階</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>11330000</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>https://www.med.jrc.or.jp/Portals/0/resources/chotatsu/zuikei/zuikei_202303q.pdf</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>製品</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>据置型デジタル式X線血管造影診断装置（Artis zee BA）（シーメンス）にかかる保守契約の締結について</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>東京都渋谷区広尾4-1-22日本赤十字社医療センター契約管財課</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>令和7年3月7日</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>シーメンスヘルスケア株式会社東京都品川区大崎1-11-1</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>19318200</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.med.jrc.or.jp/Portals/0/resources/chotatsu/zuikei/zuikei_202404q.pdf</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>血管撮影（CVS、アンギオ）</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -693,7 +779,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
     </row>
@@ -763,13 +849,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>不明（令和 6年1月 10日〜令和６年４月３０日）</t>
+          <t>不明（令和 6年1月 10日〜令和6年5月21日）</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -778,13 +864,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>不明（令和6年7月8日〜令和６年８月８日）</t>
+          <t>不明（令和6年6月5日〜令和６年７月１９日）</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -793,13 +879,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>不明（令和6年8月14日〜令和6年10月28日）</t>
+          <t>不明（令和６年８月８日〜令和6年10月28日）</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -808,7 +894,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -823,13 +909,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>不明（令和7年1月22日〜令和7年1月22日）</t>
+          <t>不明（令和7年1月22日〜令和7年2月7日）</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -838,13 +924,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>不明（令和7年 4 月 7 日〜令和7年4月1日）</t>
+          <t>不明（令和7年 4 月 7 日〜令和7年5月7日）</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -853,13 +939,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>不明（令和7年 7 月7日〜令和7年11月4日）</t>
+          <t>不明（令和7年 7 月7日〜令和7年9月19日）</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -868,13 +954,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>不明（令和7年12月25日〜令和8年1月8日）</t>
+          <t>不明（令和7年10月3日〜令和8年1月8日）</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -883,13 +969,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>不明（令和5年3月23日〜令和5年5月8日）</t>
+          <t>不明（令和5年3月23日〜令和5年6月6日）</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -898,7 +984,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
